--- a/data/mau-viec-lime.xlsx
+++ b/data/mau-viec-lime.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Ngày test (nhắc GV, chấm bài, nhập điểm, cho HS làm bù…)</t>
+          <t>Ngày test: nhắc GV tải file nghe, thu lại bài của GV</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3626,10 +3626,14 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Nhắc giáo viên tải sẵn file nghe. Nhắc giáo viên thu lại bài và gửi cho mình chấm (TUYỆT ĐỐI KHÔNG CHO GIÁO VIÊN MANG VỀ TỰ CHẤM); có thể tranh thủ chấm trong lúc trông lớp cho giáo viên đi test; nên giao thêm bài tập cho học sinh làm để dễ kiểm soát lớp hơn. Cập nhật bảng nhận xét Excel. Nhập điểm bài TEST vào file của cơ sở. Cho học sinh làm bù bài test nếu hôm lớp test có học sinh nghỉ.</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
+          <t>Nhắc giáo viên tải sẵn file nghe. Nhắc giáo viên thu lại bài và gửi cho mình chấm (TUYỆT ĐỐI KHÔNG CHO GIÁO VIÊN MANG VỀ TỰ CHẤM); có thể tranh thủ chấm trong lúc trông lớp cho giáo viên đi test; nên giao thêm bài tập cho học sinh làm để dễ kiểm soát lớp hơn.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Tách từ dòng gộp 'Ngày test (nhắc GV, chấm bài, nhập điểm, cho HS làm bù…)'</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -3637,7 +3641,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra folder tranh/thẻ chữ</t>
+          <t>Sau ngày test: chấm bài, cập nhật bảng nhận xét, nhập điểm</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Định kỳ</t>
+          <t>Ngày hôm sau ngày test</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3657,16 +3661,20 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Theo lịch định kỳ</t>
+          <t>Ngày sau ngày test của lớp</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra túi tranh / thẻ chữ theo từng unit (ví dụ Unit 1-3, 4-6, 7-9). Tổng kết thiếu tranh gì (ghi rõ tranh gì của unit nào), nhờ Media in; lấy tranh, cắt bo góc, cho vào túi tranh.</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>Chấm bài test đã thu. Cập nhật bảng nhận xét Excel. Nhập điểm bài TEST vào file của cơ sở.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Tách từ dòng gộp ngày test</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -3674,7 +3682,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Xin DS ôn bù bài tuần sau</t>
+          <t>Cho học sinh nghỉ làm bù bài test</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3684,7 +3692,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Hàng tuần</t>
+          <t>Ngày học tiếp theo của lớp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3694,16 +3702,20 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Hàng tuần, theo giáo viên (xem sheet 'Lịch lớp Yên Hòa')</t>
+          <t>Buổi học kế tiếp sau ngày test</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Xin trực tiếp các Ms ca sáng; tối nhắn tin xin các Ms dạy tối. Check lại danh sách ôn bài và tin nhắn đã hỏi. Follow đến tận khi giáo viên giao đủ bài.</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>Cho học sinh làm bù bài test nếu hôm lớp test có học sinh nghỉ.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Tách từ dòng gộp ngày test</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -3711,7 +3723,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Lịch làm key</t>
+          <t>Kiểm tra folder tranh/thẻ chữ</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3721,7 +3733,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Theo lịch BTVN</t>
+          <t>Định kỳ</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3731,20 +3743,16 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Theo lịch BTVN từng tuần (nhóm lớp Chuyên môn BTVN)</t>
+          <t>Theo lịch định kỳ</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Làm key theo lịch BTVN. Ghi bài đã làm key (ví dụ: PET Practice Test, Cam2 Unit Starter L1) và bài chưa làm thì date sang ngày hôm sau.</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Người làm: Trợ giảng/Chuyên môn</t>
-        </is>
-      </c>
+          <t>Kiểm tra túi tranh / thẻ chữ theo từng unit (ví dụ Unit 1-3, 4-6, 7-9). Tổng kết thiếu tranh gì (ghi rõ tranh gì của unit nào), nhờ Media in; lấy tranh, cắt bo góc, cho vào túi tranh.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -3752,7 +3760,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Đầu tháng: Kiểm tra + nhắc GV giao bài Khan Kids trong tháng</t>
+          <t>Xin DS ôn bù bài tuần sau</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3762,7 +3770,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Hàng tháng (đầu tháng)</t>
+          <t>Hàng tuần</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3772,13 +3780,13 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Đầu tháng</t>
+          <t>Hàng tuần, theo giáo viên (xem sheet 'Lịch lớp Yên Hòa')</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra và nhắc giáo viên giao bài Khan Kids trong tháng cho từng lớp (mỗi lớp có một mã Khan Kids). Lớp giáo viên đã giao đủ thì ghi ok; lớp chưa giao thì đã nhắc, hôm sau kiểm tra và nhắc giao bổ sung. Ghi tên người check.</t>
+          <t>Xin trực tiếp các Ms ca sáng; tối nhắn tin xin các Ms dạy tối. Check lại danh sách ôn bài và tin nhắn đã hỏi. Follow đến tận khi giáo viên giao đủ bài.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -3789,7 +3797,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Viết báo cáo + soạn văn (2 tuần 1 lần)</t>
+          <t>Lịch làm key</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3799,26 +3807,30 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>2 tuần/lần</t>
+          <t>Theo lịch BTVN</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Có (báo CM check)</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp 2 lần/tháng: L1 từ ngày 5 đến 14, L2 từ ngày 15 đến 25, ngày 26 đến 31 hoàn thành phần thiếu (xem sheet 'Lịch lớp Yên Hòa')</t>
+          <t>Theo lịch BTVN từng tuần (nhóm lớp Chuyên môn BTVN)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Viết báo cáo bài tập và soạn văn cho từng lớp theo lịch L1 / L2. Xong báo CM check. Ghi: đã xong báo cáo hay chưa, đã soạn văn hay chưa, nếu thiếu thì ngày bổ sung. Các lớp thứ 5, thứ 7, Chủ nhật chưa hoàn thành thì làm bù vào ngày tương ứng.</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
+          <t>Làm key theo lịch BTVN. Ghi bài đã làm key (ví dụ: PET Practice Test, Cam2 Unit Starter L1) và bài chưa làm thì date sang ngày hôm sau.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Người làm: Trợ giảng/Chuyên môn</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -3826,7 +3838,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Handout lỗi cần sửa</t>
+          <t>Đầu tháng: Kiểm tra + nhắc GV giao bài Khan Kids trong tháng</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3836,23 +3848,23 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Theo phát sinh</t>
+          <t>Hàng tháng (đầu tháng)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Có (up lại file báo CM check)</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Khi có handout lỗi</t>
+          <t>Đầu tháng</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Sửa handout lỗi do Chuyên môn ghi nhận. Sửa xong up lại file, báo Chuyên môn check lại, cập nhật file gốc và gửi Vận hành. Ghi: lỗi gì, sửa xong ngày nào.</t>
+          <t>Kiểm tra và nhắc giáo viên giao bài Khan Kids trong tháng cho từng lớp (mỗi lớp có một mã Khan Kids). Lớp giáo viên đã giao đủ thì ghi ok; lớp chưa giao thì đã nhắc, hôm sau kiểm tra và nhắc giao bổ sung. Ghi tên người check.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -3863,7 +3875,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Điểm danh lại HS trên phòng bù bài</t>
+          <t>Viết báo cáo + soạn văn (2 tuần 1 lần)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3873,23 +3885,23 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Hàng ngày (khi ôn bù)</t>
+          <t>2 tuần/lần</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có (báo CM check)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Ngày có ôn bù bài</t>
+          <t>Mỗi lớp 2 lần/tháng: L1 từ ngày 5 đến 14, L2 từ ngày 15 đến 25, ngày 26 đến 31 hoàn thành phần thiếu (xem sheet 'Lịch lớp Yên Hòa')</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Điểm danh lại học sinh trên phòng bù bài. Thiếu học sinh thì đi tìm hoặc gọi CSKH hỏi.</t>
+          <t>Viết báo cáo bài tập và soạn văn cho từng lớp theo lịch L1 / L2. Xong báo CM check. Ghi: đã xong báo cáo hay chưa, đã soạn văn hay chưa, nếu thiếu thì ngày bổ sung. Các lớp thứ 5, thứ 7, Chủ nhật chưa hoàn thành thì làm bù vào ngày tương ứng.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -3900,12 +3912,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Công việc phát sinh</t>
+          <t>Handout lỗi cần sửa</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Cả 2</t>
+          <t>Trợ giảng</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3915,18 +3927,18 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Tùy việc</t>
+          <t>Có (up lại file báo CM check)</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Bất kỳ lúc nào</t>
+          <t>Khi có handout lỗi</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Ai cũng thêm được. Ghi ngày phát sinh, nội dung, người làm, hạn làm. Việc chưa xong tự chuyển sang ngày làm tiếp theo.</t>
+          <t>Sửa handout lỗi do Chuyên môn ghi nhận. Sửa xong up lại file, báo Chuyên môn check lại, cập nhật file gốc và gửi Vận hành. Ghi: lỗi gì, sửa xong ngày nào.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -3937,36 +3949,110 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Công việc sự kiện</t>
+          <t>Điểm danh lại HS trên phòng bù bài</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Cả 2</t>
+          <t>Trợ giảng</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Theo sự kiện</t>
+          <t>Hàng ngày (khi ôn bù)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Tùy việc</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Theo timeline sự kiện (chuỗi 5 là mẫu ví dụ)</t>
+          <t>Ngày có ôn bù bài</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
+          <t>Điểm danh lại học sinh trên phòng bù bài. Thiếu học sinh thì đi tìm hoặc gọi CSKH hỏi.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Công việc phát sinh</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Theo phát sinh</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Tùy việc</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Bất kỳ lúc nào</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Ai cũng thêm được. Ghi ngày phát sinh, nội dung, người làm, hạn làm. Việc chưa xong tự chuyển sang ngày làm tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Công việc sự kiện</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Theo sự kiện</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Tùy việc</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Theo timeline sự kiện (chuỗi 5 là mẫu ví dụ)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
           <t>Mỗi sự kiện có timeline các đầu việc theo ngày; khi tải timeline lên thì việc tự đẩy về checklist từng đội. Mẫu ví dụ trong file: sự kiện Hồ Gươm (xem sheet 'Chuỗi theo mốc', chuỗi 5).</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3979,7 +4065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4039,7 +4125,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ngày khai giảng</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4054,7 +4140,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công tác 5 ngày trước ngày khai giảng (ghi rõ ngày + tên lớp ngay khi có thông tin lớp khai giảng): 1. Xin vào Zalo lớp. 2. Xin lesson plan (LP) của giáo viên. 3. Kiểm tra lại xem đã gửi giáo viên tài liệu khóa học chưa (syllabus, file sách, link nghe, folder BTVN, link Speaking Circle time, yêu cầu vở viết, học sinh học vượt tuổi được miễn giảm bài tập). 4. Kiểm tra lại công tác của trợ giảng và giáo viên với học sinh vượt tuổi / cần lưu ý (đã nắm được hết chưa). 5. Lập mã Khan Kids gửi giáo viên và CSKH, cập nhật vào bảng Chuyên môn, Khan Kids.</t>
+          <t>Công tác 5 ngày trước ngày khai giảng (ghi rõ ngày + tên lớp ngay khi có thông tin lớp khai giảng): xin vào Zalo lớp; xin lesson plan (LP) của giáo viên.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -4074,12 +4160,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ngày học buổi 1</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+1 ngày</t>
+          <t>-5 ngày</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4089,7 +4175,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Học buổi 1: xin giáo viên nhận xét học buổi 1 (ghi đúng ngày học sinh học, sau 1 ngày hỏi giáo viên tình hình lớp thế nào: tính cách học sinh, độ tiếp thu, cần hỗ trợ thêm gì không, kiểm tra giáo viên giao bài cẩn thận không, có video quay mẫu chưa).</t>
+          <t>Kiểm tra lại xem đã gửi giáo viên toàn bộ hệ thống tài liệu chưa: syllabus, file sách, link nghe, folder BTVN, link Speaking Circle time, yêu cầu vở viết, học sinh học vượt tuổi được miễn giảm bài tập.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4109,12 +4195,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ngày học buổi 2</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+1 ngày</t>
+          <t>-5 ngày</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4124,7 +4210,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Học buổi 2: xin giáo viên nhận xét học buổi 2 (cùng nội dung hỏi như buổi 1).</t>
+          <t>Kiểm tra lại xem đã nắm được hết chưa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4144,12 +4230,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sau 2 buổi học</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sau buổi 2</t>
+          <t>-5 ngày</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4159,7 +4245,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra tài khoản Khan Kids (giáo viên giao bài chưa, học sinh làm chưa). Tình hình bài tập (gồm cả bài KHAN và Video). Tình hình sách vở của học sinh (đủ sách và vở ghi không, biết dùng sách và vở chưa; hỏi CSKH về việc học sinh mua sách chưa; nhắn giáo viên động viên học sinh mua sách để học).</t>
+          <t>Lập mã Khan Kids gửi giáo viên và CSKH, cập nhật vào bảng Chuyên môn, Khan Kids.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4179,12 +4265,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Buổi học thứ 3 của học sinh</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Từ buổi 3</t>
+          <t>+1 ngày</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4194,7 +4280,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công tác với học sinh mới (ngay từ buổi thứ 3): học sinh có làm bài tập không (có biết làm, khó khăn gì không; cần nhắc phụ huynh cho con làm bài không).</t>
+          <t>Ghi đúng ngày học. Sau 1 ngày hỏi giáo viên tình hình lớp: tính cách học sinh, độ tiếp thu, cần hỗ trợ thêm gì không, giáo viên giao bài có cẩn thận không, đã có video quay mẫu chưa.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4214,12 +4300,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Buổi học thứ 6</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Buổi 6</t>
+          <t>+4 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4229,7 +4315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn công tác quay video sau 1 tháng. Xin nhận xét lớp luôn cho sớm. Ghi rõ ngày học buổi thứ 6 ngay từ khi có lịch lớp khai giảng.</t>
+          <t>Hỏi giáo viên cùng nội dung như buổi 1. Ngày buổi 2 theo lịch lớp.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4249,12 +4335,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ngày quay video test</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Khi quay</t>
+          <t>+5 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4264,7 +4350,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra hình thức và chất lượng quay video test của giáo viên. Check nhận xét của giáo viên.</t>
+          <t>Giáo viên đã giao bài chưa, học sinh đã làm chưa.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4284,12 +4370,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ngày khai giảng</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+1 tháng</t>
+          <t>+5 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4299,7 +4385,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Kết thúc theo dõi 1 tháng: rà soát lại toàn bộ công tác với lớp mới: video 1 tháng đủ chưa, nhận xét đủ chưa, Khan Kids, bài tập, sách vở, phản hồi của phụ huynh.</t>
+          <t>Gồm cả bài KHAN và Video.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4319,12 +4405,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ngày khai giảng</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+2,5 tháng</t>
+          <t>+5 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4334,7 +4420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Theo dõi học sinh các lớp CAM mới khai giảng / chuyển cấp độ xem có theo được lớp hay không. Ghi trước ngày bắt đầu test, test cả lớp và ghi lại kết quả vào danh sách theo dõi.</t>
+          <t>Đủ sách và vở ghi không, biết dùng sách và vở chưa. Hỏi CSKH về việc học sinh mua sách chưa; nhắn giáo viên động viên học sinh mua sách để học.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4346,65 +4432,65 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2. Học sinh mới / chuyển lớp</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Trước buổi học tiếp theo của lớp</t>
+          <t>+7 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Trợ giảng</t>
+          <t>Chuyên môn</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Hỏi Vận hành + CSKH có học sinh mới / chuyển ngang không (Chủ nhật hàng tuần). Có danh sách thì lên nội dung ôn bù bài cho học sinh, gửi Chuyên môn check, và date lịch test lại.</t>
+          <t>Học sinh có làm bài tập không (có biết làm, khó khăn gì), kiểm tra trên ảnh giáo viên. Cần nhắc phụ huynh cho con làm bài không.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Có (gửi CM check nội dung ôn bài)</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2. Học sinh mới / chuyển lớp</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu ôn</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6 buổi ôn rồi buổi thứ 7 test</t>
+          <t>+14 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Trợ giảng</t>
+          <t>Chuyên môn</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6 buổi ôn + 1 buổi test tổng hợp. Sau 6 buổi ôn thì buổi thứ 7 test lại. Nhắn hỏi giáo viên có cần ôn thêm không; BTVN đã hoàn thành đủ bài cũ chưa; kỹ năng nào ổn; kỹ năng nào vẫn cần theo dõi. Báo CM học sinh cần theo dõi.</t>
+          <t>Ghi rõ ngày học buổi thứ 6 ngay từ khi có lịch lớp khai giảng.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4416,20 +4502,20 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2. Học sinh mới / chuyển lớp</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Buổi học thứ 3 của học sinh</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Từ buổi 3</t>
+          <t>+14 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4439,7 +4525,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra các công tác với học sinh mới (hoặc học sinh chuyển lớp): tài khoản Khan Kids; sách vở; có làm bài tập không (có biết làm, khó khăn gì khi làm). Kiểm tra lịch bù bài cho học sinh, kiểm tra chéo xem trợ giảng bù bài đủ theo kế hoạch không.</t>
+          <t>Xin nhận xét lớp luôn cho sớm.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4451,20 +4537,20 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2. Học sinh mới / chuyển lớp</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ngày học thử buổi 1 / buổi 2 (học sinh chuyển lớp)</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+1 ngày</t>
+          <t>+28 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4474,7 +4560,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Học thử buổi 1 và buổi 2 (học sinh chuyển lớp): ghi đúng ngày học thử; sau 1 ngày hỏi giáo viên xem học sinh có theo được lớp không, có cần chuyển lớp khác không. Chuyên môn ghi ngày học thử + tên học sinh + tên lớp, trong phần tiến độ ghi đã xin nhận xét chưa và đã cập nhật danh sách học sinh cần theo dõi chưa. Sau buổi học thử thứ 2: trao đổi với giáo viên + test học sinh để kết luận học sinh có chuyển lớp được hay không; ghi rõ ngày và kết luận với từng học sinh.</t>
+          <t>Kiểm tra hình thức và chất lượng quay video test.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4486,20 +4572,20 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2. Học sinh mới / chuyển lớp</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Kết thúc 8 buổi đầu</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sau 8 buổi đầu</t>
+          <t>+28 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4509,7 +4595,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Cần xin nhận xét giáo viên, test học sinh, chữa nhận xét giáo viên, ghi lịch là từ buổi thứ 6. Ngày 12 hàng tháng xin CSKH danh sách học sinh. Làm theo Tuần 1, 2, 3, chi tiết như nhận xét test.</t>
+          <t>Check nhận xét của giáo viên.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4521,20 +4607,20 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Ngày 1 đến 3 hàng tháng</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Đầu tháng</t>
+          <t>+30 ngày</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -4544,7 +4630,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Chuẩn bị cho test: gửi nội dung chuyển cấp cho giáo viên từ ngày 25-28 hàng tháng, gửi cùng lịch test. Hỏi chị Alice lớp nào cần làm circle time không, có cần training không. Gửi trước cho giáo viên link nội dung bài kiểm tra và yêu cầu giáo viên cho học sinh làm quen với dạng bài và độ khó tương tự. Gửi hướng dẫn giáo viên test (link hướng dẫn cho giáo viên test sau 1 tháng: BI0, BI1 và Cam1). Cùng giáo viên thống nhất ngày quay video, báo Marketing, Quản lý, CSKH, Vận hành. Chuẩn bị phiếu cho lớp test nói.</t>
+          <t>Kết thúc theo dõi 1 tháng: rà soát lại toàn bộ công tác với lớp mới: video 1 tháng đủ chưa, nhận xét đủ chưa, Khan Kids, bài tập, sách vở, phản hồi của phụ huynh.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4556,20 +4642,20 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>1. Lớp khai giảng</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ngày 25 đến 28 hàng tháng</t>
+          <t>Ngày khai giảng (buổi học đầu tiên)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Cuối tháng</t>
+          <t>+75 ngày</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -4579,7 +4665,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật danh sách các lớp test lên nhóm LIME SCHOOL TEACHERS (ghi rõ tên lớp, bài test số, thời gian test, link). Gửi danh sách test trên nhóm, bắt các đội confirm, gửi lại thông tin bài viết báo nhóm chat LIME GIÁO VIÊN để mọi người biết có bài. Nếu sửa đổi lịch test các lớp thì comment lại lịch ở mục 'Lịch test các lớp' trong nhóm LIME SCHOOL TEACHERS và báo lại các đội CSKH, Chuyên môn, Marketing, Vận hành để đảm bảo các đội đều nắm thông tin.</t>
+          <t>Theo dõi học sinh các lớp CAM mới khai giảng / chuyển cấp độ xem có theo được lớp hay không (2,5 tháng sau khai giảng). Ghi trước ngày bắt đầu test, test cả lớp và ghi lại kết quả vào danh sách theo dõi.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4591,20 +4677,20 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ngày test</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-1 tuần</t>
+          <t>0 (ước tính)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4614,32 +4700,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra file test của lớp (1 tuần trước test): đối chiếu file test online và phiếu offline, báo Vận hành in lại bổ sung phiếu.</t>
+          <t>Hỏi Vận hành + CSKH có học sinh mới / chuyển ngang không (Chủ nhật hàng tuần). Có danh sách thì lên nội dung ôn bù bài cho học sinh (cần có trước buổi học tiếp theo của lớp), gửi Chuyên môn check nội dung ôn bài.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có (gửi CM check)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ngày test</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 (ước tính)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4649,7 +4735,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Ngày test: nhắc giáo viên tải sẵn file nghe; nhắc giáo viên thu lại bài và gửi cho mình chấm (tuyệt đối không cho giáo viên mang về tự chấm); khi check nhận xét test: dùng sổ điểm danh để kiểm tra số học sinh trong sổ điểm danh khớp với số lượng học sinh trong nhận xét test; tính lịch test, gửi file nhận xét; cập nhật bảng nhận xét Excel; nhập điểm bài test; cho học sinh làm bù bài test nếu hôm test có học sinh nghỉ.</t>
+          <t>Buổi thứ 7 test lại (đếm theo lịch lớp của bạn và lên lịch ngay từ ngày nhận được tên học sinh mới).</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4661,30 +4747,30 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ngày test</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+1 tuần</t>
+          <t>+21 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chuyên môn</t>
+          <t>Trợ giảng</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Xin giáo viên kết quả test (điểm và nhận xét): sau 1 tuần kể từ ngày test thì xin nhập điểm. Lucie xin nhận xét, check font size, số lượng; Ruby, Mai Phương check nội dung. Làm riêng cho từng cơ sở.</t>
+          <t>6 buổi ôn + 1 buổi test tổng hợp. Sau 6 buổi ôn thì buổi thứ 7 test lại; ghi lại tên bạn đã test.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4696,30 +4782,30 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ngày test</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+2 tuần</t>
+          <t>+21 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chuyên môn</t>
+          <t>Trợ giảng</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Sau 2 tuần kể từ ngày test thì xin file nhận xét (từng cơ sở).</t>
+          <t>Nhắn hỏi giáo viên có cần ôn thêm hay không; BTVN đã hoàn thành đủ hết bài cũ chưa; kỹ năng nào ổn; kỹ năng nào vẫn cần theo dõi. Ghi học sinh có cần ôn tiếp hay không.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4731,20 +4817,20 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>3. Lớp test</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Sau khi có kết quả test</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sau khi có kết quả</t>
+          <t>+7 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4754,7 +4840,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Kết thúc công tác lớp test: kiểm tra kết quả kiểm tra để đánh giá mức độ tiếp thu của lớp, đưa biện pháp khắc phục. Cập nhật bảng nhận xét sau test.</t>
+          <t>Kiểm tra tài khoản Khan Kids; sách vở (kiểm tra trên ảnh Giáo vụ); có làm bài tập không (có biết làm hay khó khăn gì, kiểm tra trên ảnh giáo viên).</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4766,20 +4852,20 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>4. Lớp chuyển cấp độ và họp phụ huynh</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ngày 25 đến 28 hàng tháng</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Cuối tháng</t>
+          <t>+7 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4789,7 +4875,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Danh sách các lớp chuyển cấp độ: trong lúc check lịch test thì tranh thủ kiểm tra xem các lớp đã bắt đầu học Unit cuối cùng chưa. Các lớp bắt đầu học bài cuối cùng là phải cho vào danh sách ngay. Hỏi chị Alice xem giáo viên cần training không, có cần gửi tài liệu Circle time không.</t>
+          <t>Kiểm tra lịch bù bài cho học sinh; kiểm tra chéo xem trợ giảng có bù bài đủ cho học sinh theo kế hoạch không.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4801,20 +4887,20 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>4. Lớp chuyển cấp độ và họp phụ huynh</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ngày có lịch họp phụ huynh</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ngay khi có lịch</t>
+          <t>+1 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -4824,7 +4910,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Chuẩn bị cho họp phụ huynh: trao đổi với giáo viên về nội dung bài kiểm tra cuối cùng và hình thức quay video; hướng dẫn giáo viên họp PH và gửi tài liệu họp; cùng giáo viên thống nhất ngày quay video, báo Marketing, Quản lý, CSKH, Vận hành; dự trù nhân sự trong buổi họp và sắp xếp phòng, báo nhóm chung; order Marketing Certificate (trước ngày họp PH đã phát chưa); lập mã Khan Kids gửi giáo viên và CSKH, cập nhật vào bảng Chuyên môn, Khan Kids.</t>
+          <t>Ghi đúng ngày học thử. Sau 1 ngày hỏi giáo viên xem học sinh có theo được lớp không, có cần chuyển lớp khác không.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4836,20 +4922,20 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>4. Lớp chuyển cấp độ và họp phụ huynh</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ngày họp phụ huynh</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Trước ngày họp</t>
+          <t>+3 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -4859,7 +4945,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Dự trù nhân sự buổi họp + xếp phòng: báo lên LIME GIÁO VỤ. Thay đổi phòng học (nếu có), nhờ vận hành nhắc thêm giáo viên khi giáo viên đến. Trước giờ họp: giáo viên hỗ trợ học sinh lên phòng khác, marketing tiếp tục trông lớp; CSKH, Vận hành phân công quét lại phòng họp, bê ghế (đếm số ghế); Alice set up máy tính và kiểm tra lại tài liệu gồm thông tin khóa học + nhận xét học sinh cuối khóa (số bản theo sĩ số lớp); sau đó họp phụ huynh. (Ví dụ trong file: họp phụ huynh lớp CAM1A lúc 19h, mốc 18h30 đến 18h45, 18h45 đến 19h.)</t>
+          <t>Hỏi giáo viên cùng nội dung như buổi 1.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4871,20 +4957,20 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>4. Lớp chuyển cấp độ và họp phụ huynh</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Ngày họp phụ huynh</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-3 buổi học (khoảng 2 tuần trước họp)</t>
+          <t>+4 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -4894,7 +4980,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Xin nhận xét cuối khóa và nhận xét học sinh đọc trong buổi họp, gửi Alice check. Làm trước ngày họp 3 buổi học (2 tuần trước họp).</t>
+          <t>Sau buổi học thử thứ 2: trao đổi với giáo viên và test học sinh để kết luận học sinh có chuyển lớp được hay không. Ghi rõ ngày và kết luận với từng học sinh.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4906,20 +4992,20 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>4. Lớp chuyển cấp độ và họp phụ huynh</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Ngày họp phụ huynh</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sau ngày họp</t>
+          <t>+28 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4929,7 +5015,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo lại kết quả cuộc họp. Đưa ra các giải pháp cho góp ý từ phụ huynh, báo nhóm chung; nếu cần thực hiện công việc gì thì thêm vào CVPS. Gửi phụ huynh tóm tắt nội dung buổi họp phụ huynh.</t>
+          <t>Xin nhận xét giáo viên sau 8 buổi đầu.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4941,20 +5027,20 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>4. Lớp chuyển cấp độ và họp phụ huynh</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Ngày lớp bắt đầu khóa mới</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sau 2 buổi đầu</t>
+          <t>+28 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4964,7 +5050,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra tài khoản Khan Kids (giáo viên giao bài chưa, học sinh làm chưa). Tình hình bài tập (gồm cả bài Khan và Video). Tình hình sách vở của học sinh (đủ sách và vở ghi, biết dùng sách và vở chưa; hỏi CSKH học sinh mua sách chưa; nhắn giáo viên động viên học sinh mua sách). Theo dõi tình hình đáp ứng khóa mới của giáo viên và học sinh.</t>
+          <t>Test học sinh sau 8 buổi đầu.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4976,20 +5062,20 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>2. Học sinh mới / chuyển lớp</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày nhận danh sách học sinh mới / chuyển ngang</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12 đến -10 ngày</t>
+          <t>+29 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4999,7 +5085,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Tạo bộ câu hỏi theo chủ đề sự kiện (ví dụ trong file: bộ câu hỏi chủ đề Phụ nữ Việt Nam).</t>
+          <t>Chữa nhận xét giáo viên.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5011,30 +5097,30 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-10 đến -8 ngày</t>
+          <t>-20 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bộ phận Media</t>
+          <t>Chuyên môn</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Media đăng video truyền thông.</t>
+          <t>Gửi nội dung chuyển cấp cho giáo viên (từ ngày 25-28 hàng tháng), gửi cùng lịch test. Hỏi chị Alice lớp nào cần làm circle time không, có cần training không.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5046,20 +5132,20 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7 ngày</t>
+          <t>-20 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -5069,7 +5155,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Chốt đăng ký lần 1 và tổng hợp lại nội dung luyện tập gửi lại phụ huynh.</t>
+          <t>Gửi trước cho giáo viên link nội dung bài kiểm tra và yêu cầu giáo viên cho học sinh làm quen với dạng bài và độ khó tương tự.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -5081,30 +5167,30 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-6 đến -5 ngày</t>
+          <t>-20 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Quản lý / người phụ trách</t>
+          <t>Chuyên môn</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tìm nhân sự cho sự kiện.</t>
+          <t>Gửi link hướng dẫn cho giáo viên test sau 1 tháng (BI0, BI1 và Cam1).</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5116,20 +5202,20 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4 ngày</t>
+          <t>-14 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -5139,7 +5225,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Chốt đăng ký lần cuối.</t>
+          <t>Ghi rõ tên lớp, bài test số, thời gian test, link. Cập nhật từ ngày 25-28 hàng tháng.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -5151,20 +5237,20 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-3 ngày</t>
+          <t>-14 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5174,7 +5260,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Họp và gửi tài liệu cho nhân sự.</t>
+          <t>Nếu sửa đổi lịch test các lớp thì comment lại ở mục 'Lịch test các lớp' trong nhóm LIME SCHOOL TEACHERS và báo lại các đội CSKH, Chuyên môn, Marketing, Vận hành để đảm bảo các đội đều nắm thông tin.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5186,20 +5272,20 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-2 ngày</t>
+          <t>-14 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -5209,7 +5295,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Chuẩn bị thẻ và in tài liệu.</t>
+          <t>Gửi lại thông tin bài viết báo nhóm chat LIME GIÁO VIÊN để mọi người biết có bài.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5221,30 +5307,30 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ngày diễn ra sự kiện</t>
+          <t>Ngày test của lớp</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-2 đến -1 ngày</t>
+          <t>-14 ngày (ước tính)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CSKH</t>
+          <t>Chuyên môn</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>CSKH gửi phụ huynh địa điểm sự kiện.</t>
+          <t>Cùng giáo viên thống nhất ngày quay video, báo Marketing, Quản lý, CSKH, Vận hành.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5256,33 +5342,1573 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>5. Sự kiện (mẫu ví dụ: Hồ Gươm)</t>
+          <t>3. Lớp test</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-14 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Chuẩn bị phiếu cho lớp test nói.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-7 ngày</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Trợ giảng</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Đối chiếu file test online và phiếu offline. Nếu khác thì báo Vận hành in lại bổ sung phiếu.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Trợ giảng</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Nhắc giáo viên tải sẵn file nghe trước giờ test.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Trợ giảng</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Nhắc giáo viên thu lại bài và gửi cho mình chấm (TUYỆT ĐỐI KHÔNG CHO GIÁO VIÊN MANG VỀ TỰ CHẤM). Có thể trông lớp cho giáo viên đi test; nên giao thêm bài tập cho học sinh làm để dễ kiểm soát lớp hơn.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>+1 ngày</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Trợ giảng</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Chấm bài test đã thu hôm trước (không để giáo viên mang về tự chấm).</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>+1 ngày</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Trợ giảng</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Nhập điểm bài TEST vào file của cơ sở; cập nhật bảng nhận xét Excel.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>+3 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Trợ giảng</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Nếu hôm lớp test có học sinh nghỉ thì cho học sinh làm bù bài test (theo ngày học tiếp theo của lớp).</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>+7 ngày</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Sau 1 tuần kể từ ngày test thì xin giáo viên điểm.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>+7 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Lucie xin nhận xét, check font size, số lượng; Ruby, Mai Phương check nội dung. Làm riêng cho từng cơ sở.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>+14 ngày</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Sau 2 tuần kể từ ngày test thì xin file nhận xét (từng cơ sở). Khi check nhận xét test: dùng sổ điểm danh để kiểm tra số học sinh khớp với số lượng học sinh trong nhận xét test.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>+15 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Kết thúc công tác lớp test: kiểm tra kết quả kiểm tra để đánh giá mức độ tiếp thu của lớp, đưa biện pháp khắc phục.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>3. Lớp test</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Ngày test của lớp</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>+15 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật bảng nhận xét sau test.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>-21 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Trong lúc check lịch test (ngày 25-28) tranh thủ kiểm tra xem các lớp đã bắt đầu học Unit cuối cùng chưa. Lớp bắt đầu học bài cuối cùng là phải cho vào danh sách lớp chuyển cấp độ ngay.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>-21 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Hỏi chị Alice xem giáo viên cần training không, có cần gửi tài liệu Circle time không.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>-14 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Làm trước ngày họp 3 buổi học (2 tuần trước họp).</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>-12 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Gửi Alice check nhận xét cuối khóa và nhận xét học sinh đọc trong buổi họp.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>-14 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi với giáo viên về nội dung bài kiểm tra cuối cùng và hình thức quay video.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>-7 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Hướng dẫn giáo viên họp PH và gửi tài liệu họp.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-7 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Báo Marketing, Quản lý, CSKH, Vận hành.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>-7 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra trước ngày họp PH đã phát chưa.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>-3 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Lập mã Khan Kids gửi giáo viên và CSKH, cập nhật vào bảng Chuyên môn, Khan Kids.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>-3 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Thay đổi phòng học (nếu có), nhờ Vận hành nhắc thêm giáo viên khi giáo viên đến.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên hỗ trợ học sinh lên phòng khác, Marketing tiếp tục trông lớp.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>CSKH, Vận hành phân công quét lại phòng họp, bê ghế (đếm số ghế).</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Alice set up máy tính và kiểm tra lại tài liệu gồm thông tin khóa học + nhận xét học sinh cuối khóa (số bản theo sĩ số lớp).</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Ví dụ trong file: họp phụ huynh lớp CAM1A lúc 19h, các mốc chuẩn bị 18h30 đến 18h45 và 18h45 đến 19h.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>+1 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo lại kết quả cuộc họp.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>+1 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Đưa ra các giải pháp cho góp ý từ phụ huynh, báo nhóm chung; nếu cần thực hiện công việc gì thì thêm vào CVPS.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>+1 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Gửi phụ huynh tóm tắt nội dung buổi họp phụ huynh.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>+10 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên giao bài chưa, học sinh làm chưa.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>+10 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Gồm cả bài Khan và Video.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>+10 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Đủ sách và vở ghi, biết dùng sách và vở chưa; hỏi CSKH học sinh mua sách chưa; nhắn giáo viên động viên học sinh mua sách để học.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>4. Lớp chuyển cấp độ + họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Ngày họp phụ huynh</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>+10 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Theo dõi tình hình đáp ứng khóa mới của giáo viên và học sinh.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Ngày diễn ra sự kiện</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>-12 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Ví dụ trong file: bộ câu hỏi chủ đề Phụ nữ Việt Nam.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>-10 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Bộ phận Media đăng video truyền thông.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>-7 ngày</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Chốt đăng ký lần 1.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>-7 ngày</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Tổng hợp lại nội dung luyện tập gửi lại phụ huynh.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>-6 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Quản lý / người phụ trách tìm nhân sự cho sự kiện.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>-4 ngày</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Chốt đăng ký lần cuối.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>-3 ngày</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Họp với nhân sự tham gia sự kiện.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>-3 ngày</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Gửi tài liệu cho nhân sự.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>-2 ngày</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Chuẩn bị thẻ.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>-2 ngày</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên môn</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>In tài liệu.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>-2 ngày (ước tính)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Cả 2</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>CSKH gửi phụ huynh địa điểm sự kiện.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>5. Sự kiện (mẫu: Hồ Gươm)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Ngày diễn ra sự kiện</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Cả 2</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Sự kiện diễn ra.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
